--- a/www/download/IND.hours_worked.empe.s.hr.zdW16.xlsx
+++ b/www/download/IND.hours_worked.empe.s.hr.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>14013.16</t>
+          <t>14013160000</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14009.876</t>
+          <t>14009876000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14312.324</t>
+          <t>14312324000</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14633.962</t>
+          <t>14633962000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>15189.58</t>
+          <t>15189580000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>15732.532</t>
+          <t>15732532000</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16355.367</t>
+          <t>16355367000</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>16687.979</t>
+          <t>16687979000</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>16433.831</t>
+          <t>16433831000</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>17148.781</t>
+          <t>17148781000</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>17250.386</t>
+          <t>17250386000</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>17886.616</t>
+          <t>17886616000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>17957.596</t>
+          <t>17957596000</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>18149.227</t>
+          <t>18149227000</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>18445.658</t>
+          <t>18445658000</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5384.854</t>
+          <t>5384854000</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5395.217</t>
+          <t>5395217000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5368.603</t>
+          <t>5368603000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>5374.061</t>
+          <t>5374061000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5422.009</t>
+          <t>5422009000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5448.22</t>
+          <t>5448220000</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5489.266</t>
+          <t>5489266000</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5593.98</t>
+          <t>5593980000</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>5715.131</t>
+          <t>5715131000</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>5497.263</t>
+          <t>5497263000</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5549.865</t>
+          <t>5549865000</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>5651.305</t>
+          <t>5651305000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5688.356</t>
+          <t>5688356000</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>5686.141</t>
+          <t>5686141000</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5729.812</t>
+          <t>5729812000</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4972.022</t>
+          <t>4972022000</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5046.563</t>
+          <t>5046563000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5019.687</t>
+          <t>5019687000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5016.187</t>
+          <t>5016187000</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5074.917</t>
+          <t>5074917000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5141.645</t>
+          <t>5141645000</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5207.967</t>
+          <t>5207967000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>5311.215</t>
+          <t>5311215000</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5394.065</t>
+          <t>5394065000</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>5290.562</t>
+          <t>5290562000</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>5320.788</t>
+          <t>5320788000</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>5434.913</t>
+          <t>5434913000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>5449.255</t>
+          <t>5449255000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5407.5</t>
+          <t>5407500000</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5424.248</t>
+          <t>5424248000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4052.673</t>
+          <t>4052673000</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4053.491</t>
+          <t>4053491000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4045.796</t>
+          <t>4045796000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4139.088</t>
+          <t>4139088000</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4269.04</t>
+          <t>4269040000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4358.348</t>
+          <t>4358348000</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4547.328</t>
+          <t>4547328000</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4737.114</t>
+          <t>4737114000</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5004.953</t>
+          <t>5004953000</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4733.784</t>
+          <t>4733784000</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>4478.89</t>
+          <t>4478890000</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>4385.134</t>
+          <t>4385134000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>4277.545</t>
+          <t>4277545000</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>4244.452</t>
+          <t>4244452000</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>4451.226</t>
+          <t>4451226000</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>147586.76</t>
+          <t>147586760000</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150219.519</t>
+          <t>150219519000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>154195.149</t>
+          <t>154195149000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>162195.703</t>
+          <t>162195703000</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>170243.617</t>
+          <t>170243617000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>175636.448</t>
+          <t>175636448000</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>180026.749</t>
+          <t>180026749000</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>188347.258</t>
+          <t>188347258000</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>187052.339</t>
+          <t>187052339000</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>180756.587</t>
+          <t>180756587000</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>184158.57</t>
+          <t>184158570000</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>189584.217</t>
+          <t>189584217000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>189252.988</t>
+          <t>189252988000</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>199590.815</t>
+          <t>199590815000</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>201311.206</t>
+          <t>201311206000</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>23762.843</t>
+          <t>23762843000</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24094.571</t>
+          <t>24094571000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24531.374</t>
+          <t>24531374000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>24968.62</t>
+          <t>24968620000</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25608.669</t>
+          <t>25608669000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25863.386</t>
+          <t>25863386000</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26327.656</t>
+          <t>26327656000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>26871.221</t>
+          <t>26871221000</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>27635.016</t>
+          <t>27635016000</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>25891.954</t>
+          <t>25891954000</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>26494.092</t>
+          <t>26494092000</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>26772.168</t>
+          <t>26772168000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>27378.325</t>
+          <t>27378325000</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>27689.923</t>
+          <t>27689923000</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>28745.641</t>
+          <t>28745641000</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>484058.712</t>
+          <t>484058712196.965</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>524443.508</t>
+          <t>524443507580.079</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>563971.475</t>
+          <t>563971475298.109</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>593106.096</t>
+          <t>593106096064.014</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>617370.28</t>
+          <t>617370279587.777</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>633936.541</t>
+          <t>633936540633.373</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>640117.6</t>
+          <t>640117599753.073</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>664178.389</t>
+          <t>664178388837.835</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>698883.052</t>
+          <t>698883051759.265</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>722777.373</t>
+          <t>722777372945.087</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>739113.132</t>
+          <t>739113131531.172</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>818465.66</t>
+          <t>818465660151.383</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>849329.316</t>
+          <t>849329315738.673</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>871572.643</t>
+          <t>871572642855.397</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>889206.516</t>
+          <t>889206516354.598</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>423.511</t>
+          <t>423511000</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>436.468</t>
+          <t>436468000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>446.083</t>
+          <t>446083000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>458.106</t>
+          <t>458106000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>462.009</t>
+          <t>462009000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>472.919</t>
+          <t>472919000</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>497.108</t>
+          <t>497108000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>519.421</t>
+          <t>519421000</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>556.486</t>
+          <t>556486000</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>554.817</t>
+          <t>554817000</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>557.869</t>
+          <t>557869000</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>560.349</t>
+          <t>560349000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>540.638</t>
+          <t>540638000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>506.844</t>
+          <t>506844000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>492.319</t>
+          <t>492319000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7503.32</t>
+          <t>7503320000</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7128.206</t>
+          <t>7128206000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7068.005</t>
+          <t>7068005000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6859.997</t>
+          <t>6859997000</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>6969614000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>7215308000</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>7246877000</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>7395330000</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>7603847000</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>7406866000</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>7361172000</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>7360.311</t>
+          <t>7360311000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>7355.239</t>
+          <t>7355239000</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>7406.026</t>
+          <t>7406026000</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>7472.025</t>
+          <t>7472025000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>48833</t>
+          <t>4.8833e+10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>48420</t>
+          <t>4.842e+10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>47834</t>
+          <t>4.7834e+10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46977</t>
+          <t>4.6977e+10</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>4.6814e+10</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>46211</t>
+          <t>4.6211e+10</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>47231</t>
+          <t>4.7231e+10</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>4.8198e+10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>4.8697e+10</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>46937</t>
+          <t>4.6937e+10</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>47843</t>
+          <t>4.7843e+10</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>48666</t>
+          <t>4.8666e+10</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>48785</t>
+          <t>4.8785e+10</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>4.8868e+10</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>49721</t>
+          <t>4.9721e+10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3625.842</t>
+          <t>3625842000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3682.792</t>
+          <t>3682792000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3651.101</t>
+          <t>3651101000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3607.169</t>
+          <t>3607169000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3600.217</t>
+          <t>3600217000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3651.787</t>
+          <t>3651787000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3752.763</t>
+          <t>3752763000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3795.767</t>
+          <t>3795767000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3845.516</t>
+          <t>3845516000</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3715.175</t>
+          <t>3715175000</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>3606.58</t>
+          <t>3606580000</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>3649.161</t>
+          <t>3649161000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3587.407</t>
+          <t>3587407000</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>3643.337</t>
+          <t>3643337000</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>3681.438</t>
+          <t>3681438000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23621.694</t>
+          <t>23621694000</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24701.869</t>
+          <t>24701869000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25565.822</t>
+          <t>25565822000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>26488.219</t>
+          <t>26488219000</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>27358.158</t>
+          <t>27358158000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>28448.156</t>
+          <t>28448156000</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>29650.56</t>
+          <t>29650560000</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>30541.522</t>
+          <t>30541522000</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>30781.581</t>
+          <t>30781581000</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>29022.181</t>
+          <t>29022181000</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>28418.43</t>
+          <t>28418430000</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>27720.345</t>
+          <t>27720344700</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>26150.167</t>
+          <t>26150167500</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>25162.207</t>
+          <t>25162206500</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>25534.535</t>
+          <t>25534534600</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1042.838</t>
+          <t>1042838000</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1057.137</t>
+          <t>1057137000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1054.244</t>
+          <t>1054244000</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1079.232</t>
+          <t>1079232000</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1070.003</t>
+          <t>1070003000</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1134.384</t>
+          <t>1134384000</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1178.243</t>
+          <t>1178243000</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1167.145</t>
+          <t>1167145000</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1162.127</t>
+          <t>1162127000</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>972.034</t>
+          <t>972034000</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>941.215</t>
+          <t>941215000</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1025.968</t>
+          <t>1025968000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1002.652</t>
+          <t>1002652000</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1019.821</t>
+          <t>1019821000</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1040.607</t>
+          <t>1040607000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3283.9</t>
+          <t>3283900000</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3327.2</t>
+          <t>3327200000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3.362e+09</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3.364e+09</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3388.2</t>
+          <t>3388200000</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3427.8</t>
+          <t>3427800000</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3483.1</t>
+          <t>3483100000</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>3561.4</t>
+          <t>3561400000</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>3636.5</t>
+          <t>3636500000</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3472.1</t>
+          <t>3472100000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>3473.5</t>
+          <t>3473500000</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>3518.6</t>
+          <t>3518600000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3522.5</t>
+          <t>3522500000</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3495.3</t>
+          <t>3495300000</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3.462e+09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>33668.202</t>
+          <t>33668202000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>34113.125</t>
+          <t>34113125000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>33486.152</t>
+          <t>33486152000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>33417.848</t>
+          <t>33417848000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>34100.736</t>
+          <t>34100736000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>34206.04</t>
+          <t>34206040000</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>34052.701</t>
+          <t>34052701000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34960.624</t>
+          <t>34960624000</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>35343.671</t>
+          <t>35343671000</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>34475.606</t>
+          <t>34475606000</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>34548.595</t>
+          <t>34548595000</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>34785.535</t>
+          <t>34785535000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>34667.971</t>
+          <t>34667971000</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>34252.927</t>
+          <t>34252927000</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>34307.826</t>
+          <t>34307826000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>40619.228</t>
+          <t>40619228000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>40936.533</t>
+          <t>40936533000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40901.692</t>
+          <t>40901692000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40782.353</t>
+          <t>40782353000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40825.354</t>
+          <t>40825354000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>41818.452</t>
+          <t>41818452000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>42012.411</t>
+          <t>42012411000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>42413.228</t>
+          <t>42413228000</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>42235.907</t>
+          <t>42235907000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>41343.691</t>
+          <t>41343691000</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>41269.384</t>
+          <t>41269384000</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>41448.212</t>
+          <t>41448212000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>42174.181</t>
+          <t>42174181000</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>42943.732</t>
+          <t>42943732000</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>43877.235</t>
+          <t>43877235000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5318.839</t>
+          <t>5318839100</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5428.968</t>
+          <t>5428968500</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5635.053</t>
+          <t>5635052800</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5757.773</t>
+          <t>5757773200</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5916.714</t>
+          <t>5916714100</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>6109.817</t>
+          <t>6109817400</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6303.115</t>
+          <t>6303115400</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6480.266</t>
+          <t>6480265600</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>6592.1</t>
+          <t>6592100100</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>6491.208</t>
+          <t>6491208300</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>6130.236</t>
+          <t>6130235900</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>5668.764</t>
+          <t>5668764100</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>5286.824</t>
+          <t>5286824000</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>5076.474</t>
+          <t>5076474500</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>5009.031</t>
+          <t>5009031100</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7043.947</t>
+          <t>7043947000</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7028.262</t>
+          <t>7028262000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>7096.729</t>
+          <t>7096729000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7084.115</t>
+          <t>7084115000</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7141.998</t>
+          <t>7141998000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7232.103</t>
+          <t>7232103000</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>7293.256</t>
+          <t>7293256000</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>7320.774</t>
+          <t>7320774000</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>7200.055</t>
+          <t>7200055000</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>6978.606</t>
+          <t>6978606000</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>6247.67</t>
+          <t>6247670000</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>6244.206</t>
+          <t>6244206000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>6179.156</t>
+          <t>6179156000</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>6282.516</t>
+          <t>6282516000</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>6639.684</t>
+          <t>6639684000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>68936.963</t>
+          <t>68936963000</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>74522.705</t>
+          <t>74522705000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78386.638</t>
+          <t>78386638000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>77871.127</t>
+          <t>77871127000</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>82806.33</t>
+          <t>82806330000</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>72426.913</t>
+          <t>72426913000</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>68493.533</t>
+          <t>68493533000</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>68041.404</t>
+          <t>68041404000</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>68774.789</t>
+          <t>68774789000</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>70833.183</t>
+          <t>70833183000</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>76726.992</t>
+          <t>76726992000</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>80070.701</t>
+          <t>80070701000</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>89154.68</t>
+          <t>89154680000</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>99676.829</t>
+          <t>99676829000</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>111104.239</t>
+          <t>111104239000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>445332.627</t>
+          <t>445332627000</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>449907.673</t>
+          <t>449907673000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>454652.7</t>
+          <t>454652700000</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>460906.026</t>
+          <t>460906026000</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>469523.859</t>
+          <t>469523859000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>481211.636</t>
+          <t>481211636000</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>493947.562</t>
+          <t>493947562000</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>508653.299</t>
+          <t>508653299000</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>523074.027</t>
+          <t>523074027000</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>539838.332</t>
+          <t>539838332000</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>542896.428</t>
+          <t>542896428000</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>545686.993</t>
+          <t>545686993000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>614660.341</t>
+          <t>614660341000</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>688095.379</t>
+          <t>688095379000</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>747929.795</t>
+          <t>747929795000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2614.474</t>
+          <t>2614474000</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2694.332</t>
+          <t>2694332000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2714.471</t>
+          <t>2714471000</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2754.193</t>
+          <t>2754193000</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2825.752</t>
+          <t>2825752000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3011.362</t>
+          <t>3011362000</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3178.716</t>
+          <t>3178716000</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3263.874</t>
+          <t>3263874000</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>3188.589</t>
+          <t>3188589000</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2891.487</t>
+          <t>2891487000</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2766.921</t>
+          <t>2766921000</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>2735.885</t>
+          <t>2735885000</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2731.447</t>
+          <t>2731447000</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2780.543</t>
+          <t>2780543000</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2838.109</t>
+          <t>2838109000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>28269.982</t>
+          <t>28269982000</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>28718.064</t>
+          <t>28718064000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29107.791</t>
+          <t>29107791000</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>29121.067</t>
+          <t>29121067000</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>29263.41</t>
+          <t>29263410000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>29569.637</t>
+          <t>29569637000</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>30318.697</t>
+          <t>30318697000</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>30783.622</t>
+          <t>30783622000</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>31022.793</t>
+          <t>31022793000</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>29969.796</t>
+          <t>29969796000</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>29636.325</t>
+          <t>29636325000</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>29756.257</t>
+          <t>29756257000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>29059.891</t>
+          <t>29059891000</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>28323.992</t>
+          <t>28323992000</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>28416.143</t>
+          <t>28416143000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>99508.392</t>
+          <t>99508392440</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>98380.036</t>
+          <t>98380036127</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96354.936</t>
+          <t>96354936371</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>96365.669</t>
+          <t>96365669024</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>96723.76</t>
+          <t>96723760485</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>96839.829</t>
+          <t>96839829232</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>98632.02</t>
+          <t>98632019923</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>99149.193</t>
+          <t>99149193041</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>98093.174</t>
+          <t>98093173730</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>94098.707</t>
+          <t>94098707348</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>95242.37</t>
+          <t>95242370129</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>95002.359</t>
+          <t>95002359474</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>95308.515</t>
+          <t>95308514777</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>94708.474</t>
+          <t>94708474005</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>93356.966</t>
+          <t>93356965570</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24988.067</t>
+          <t>24988067000</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25316.651</t>
+          <t>25316651000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26057.719</t>
+          <t>26057719000</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27118.676</t>
+          <t>27118676000</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29344.074</t>
+          <t>29344074000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>28960.863</t>
+          <t>28960863000</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>29634.688</t>
+          <t>29634688000</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>29652.591</t>
+          <t>29652591000</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>30061.072</t>
+          <t>30061072000</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>32249.661</t>
+          <t>32249661000</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>33042.143</t>
+          <t>33042143000</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>34526.728</t>
+          <t>34526728000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>34876.022</t>
+          <t>34876022000</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>36450.896</t>
+          <t>36450896000</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>37024.12</t>
+          <t>37024120000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2079.099</t>
+          <t>2079099000</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1980.797</t>
+          <t>1980797000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2021.935</t>
+          <t>2021935000</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2056.135</t>
+          <t>2056135000</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2173.845</t>
+          <t>2173845000</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2215.233</t>
+          <t>2215233000</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2210.973</t>
+          <t>2210973000</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2351.82</t>
+          <t>2351820000</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2420.548</t>
+          <t>2420548000</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2150.535</t>
+          <t>2150535000</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2086.026</t>
+          <t>2086026000</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2070.567</t>
+          <t>2070567000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2094.47</t>
+          <t>2094470000</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2090.673</t>
+          <t>2090673000</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2115.612</t>
+          <t>2115612000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>391.961</t>
+          <t>391961000</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>413.078</t>
+          <t>413078000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>424.934</t>
+          <t>424934000</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>432.036</t>
+          <t>432036000</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>441.649</t>
+          <t>441649000</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>447.886</t>
+          <t>447886000</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>466.147</t>
+          <t>466147000</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>491.041</t>
+          <t>491041000</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>514.935</t>
+          <t>514935000</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>503.329</t>
+          <t>503329000</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>513.946</t>
+          <t>513946000</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>528.725</t>
+          <t>528725000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>538.872</t>
+          <t>538872000</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>551.023</t>
+          <t>551023000</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>575.236</t>
+          <t>575236000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1535.709</t>
+          <t>1535709000</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1571.557</t>
+          <t>1571557000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1589.281</t>
+          <t>1589281000</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1615.794</t>
+          <t>1615794000</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1583.963</t>
+          <t>1583963000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1634.536</t>
+          <t>1634536000</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1728.467</t>
+          <t>1728467000</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1770.056</t>
+          <t>1770056000</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1880.672</t>
+          <t>1880672000</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1541.993</t>
+          <t>1541993000</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1420.831</t>
+          <t>1420831000</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1454.661</t>
+          <t>1454661000</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1491.285</t>
+          <t>1491285000</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1509.355</t>
+          <t>1509355000</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1520.214</t>
+          <t>1520214000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45028.956</t>
+          <t>45028956000</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>44016.188</t>
+          <t>44016188000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>44192.875</t>
+          <t>44192875000</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>47127.747</t>
+          <t>47127747000</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>49012.635</t>
+          <t>49012635000</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>49276.815</t>
+          <t>49276815000</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>51115.588</t>
+          <t>51115588000</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>52515.988</t>
+          <t>52515988000</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>53341.374</t>
+          <t>53341374000</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>51630.229</t>
+          <t>51630229000</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>52437.734</t>
+          <t>52437734000</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>53275.677</t>
+          <t>53275677000</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>54650.62</t>
+          <t>54650620000</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>54220.142</t>
+          <t>54220142000</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>54796.975</t>
+          <t>54796975000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>279.487</t>
+          <t>279487000</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>268.753</t>
+          <t>268753000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>277.871</t>
+          <t>277871000</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>277.043</t>
+          <t>277043000</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>262.675</t>
+          <t>262675000</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>277.219</t>
+          <t>277219000</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>275.867</t>
+          <t>275867000</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>285.294</t>
+          <t>285294000</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>304.514</t>
+          <t>304514000</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>292.19</t>
+          <t>292190000</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>297.223</t>
+          <t>297223000</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>300.784</t>
+          <t>300784000</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>302.355</t>
+          <t>302355000</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>305.79</t>
+          <t>305790000</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>317.023</t>
+          <t>317023000</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>9683.639</t>
+          <t>9683639200</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9889.248</t>
+          <t>9889247500</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9874.277</t>
+          <t>9874277000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>9784.673</t>
+          <t>9784672800</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>9757.916</t>
+          <t>9757915600</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9669.388</t>
+          <t>9669387800</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>9794.894</t>
+          <t>9794894200</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>10046.648</t>
+          <t>10046647600</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>10249.08</t>
+          <t>10249080200</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>10080.537</t>
+          <t>10080536600</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>9969.996</t>
+          <t>9969995700</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>10043.639</t>
+          <t>10043638700</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>9909.044</t>
+          <t>9909044400</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>9780.974</t>
+          <t>9780974000</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>9750.111</t>
+          <t>9750110700</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22459.987</t>
+          <t>22459987000</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>21432.975</t>
+          <t>21432975000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20556.203</t>
+          <t>20556203000</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20392.317</t>
+          <t>20392317000</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20794.768</t>
+          <t>20794768000</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>21478.274</t>
+          <t>21478274000</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>22538.087</t>
+          <t>22538087000</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>23853.77</t>
+          <t>23853770000</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>24851.878</t>
+          <t>24851878000</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>24823.243</t>
+          <t>24823243000</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>24134.532</t>
+          <t>24134532000</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>24195.665</t>
+          <t>24195665000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>24283.618</t>
+          <t>24283618000</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>24309.245</t>
+          <t>24309245000</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>24813.758</t>
+          <t>24813758000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7613.067</t>
+          <t>7613067000</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7690.033</t>
+          <t>7690033000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7744.403</t>
+          <t>7744403000</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>7647.665</t>
+          <t>7647665000</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7699.433</t>
+          <t>7699433000</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7709.024</t>
+          <t>7709024000</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7764.62</t>
+          <t>7764620000</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>7829.745</t>
+          <t>7829745000</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>7838.12</t>
+          <t>7838120000</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>7679.032</t>
+          <t>7679032000</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>7667.207</t>
+          <t>7667207000</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>7416.264</t>
+          <t>7416264000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>7013.685</t>
+          <t>7013685000</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>6909.289</t>
+          <t>6909289000</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>7069.171</t>
+          <t>7069171000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>11408.567</t>
+          <t>11408567000</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>11290.436</t>
+          <t>11290436000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11921.931</t>
+          <t>11921931000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11554.795</t>
+          <t>11554795000</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>12478.508</t>
+          <t>12478508000</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>11990.175</t>
+          <t>11990175000</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>12362.531</t>
+          <t>12362531000</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>12500.772</t>
+          <t>12500772000</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>12607212000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>1.2044e+10</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>11459.093</t>
+          <t>11459093000</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>12042.35</t>
+          <t>12042350000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11191.338</t>
+          <t>11191338000</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>11156.219</t>
+          <t>11156219000</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>11688.135</t>
+          <t>11688135000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>113791.683</t>
+          <t>113791683000</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>112933.372</t>
+          <t>112933372000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>113069.898</t>
+          <t>113069898000</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>113275.945</t>
+          <t>113275945000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>114351.922</t>
+          <t>114351922000</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>116707.602</t>
+          <t>116707602000</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>117843.623</t>
+          <t>117843623000</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>119010.842</t>
+          <t>119010842000</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>111583.096</t>
+          <t>111583096000</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>107752.964</t>
+          <t>107752964000</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>107975.668</t>
+          <t>107975668000</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>107391.548</t>
+          <t>107391548000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>109117.823</t>
+          <t>109117823000</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>106107.939</t>
+          <t>106107939000</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>104932.646</t>
+          <t>104932646000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3149.145</t>
+          <t>3149145000</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3147.712</t>
+          <t>3147712000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3048.128</t>
+          <t>3048128000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2953.589</t>
+          <t>2953589000</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2958.433</t>
+          <t>2958433000</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3040.162</t>
+          <t>3040162000</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3098.051</t>
+          <t>3098051000</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3160.638</t>
+          <t>3160638000</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3235.005</t>
+          <t>3235005000</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3093.644</t>
+          <t>3093644000</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>3100.7</t>
+          <t>3100700000</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>3160.662</t>
+          <t>3160662000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>3171.324</t>
+          <t>3171324000</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>3127.058</t>
+          <t>3127058000</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>3177.435</t>
+          <t>3177435000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1189.232</t>
+          <t>1189232000</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1192.581</t>
+          <t>1192581000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1248.047</t>
+          <t>1248047000</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1256.695</t>
+          <t>1256695000</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1284.726</t>
+          <t>1284726000</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1251.254</t>
+          <t>1251254000</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1255.526</t>
+          <t>1255526000</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1291.599</t>
+          <t>1291599000</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1337.518</t>
+          <t>1337518000</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1313.15</t>
+          <t>1313150000</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1290.35</t>
+          <t>1290350000</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1252.858</t>
+          <t>1252858000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1214.124</t>
+          <t>1214124000</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1194.287</t>
+          <t>1194287000</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1212.155</t>
+          <t>1212155000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6528.524</t>
+          <t>6528524000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6608.288</t>
+          <t>6608288000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6526.947</t>
+          <t>6526947000</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>6447.867</t>
+          <t>6447867000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6494.826</t>
+          <t>6494826000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6497.448</t>
+          <t>6497448000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6592.548</t>
+          <t>6592548000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6800.544</t>
+          <t>6800544000</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6920.436</t>
+          <t>6920436000</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6706.98</t>
+          <t>6706980000</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>6885.54</t>
+          <t>6885540000</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>7045.836</t>
+          <t>7045836000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>7049.849</t>
+          <t>7049849000</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>7092.37</t>
+          <t>7092370000</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>7215.88</t>
+          <t>7215880000</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23619.242</t>
+          <t>23619242000</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>22938.392</t>
+          <t>22938392000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>22836.392</t>
+          <t>22836392000</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22730.842</t>
+          <t>22730842000</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>22948.406</t>
+          <t>22948406000</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>24402.524</t>
+          <t>24402524000</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>24476.351</t>
+          <t>24476351000</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>24210.686</t>
+          <t>24210686000</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>24855.65</t>
+          <t>24855650000</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>24383.023</t>
+          <t>24383023000</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>25875.796</t>
+          <t>25875796000</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>27502.09</t>
+          <t>27502090000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>30129.227</t>
+          <t>30129227000</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>33306.843</t>
+          <t>33306843000</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>37712.431</t>
+          <t>37712431000</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>15199.571</t>
+          <t>15199571000</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>14088.907</t>
+          <t>14088907000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>14066.893</t>
+          <t>14066893000</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>14498.192</t>
+          <t>14498192000</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>15201.776</t>
+          <t>15201776000</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>15418.961</t>
+          <t>15418961000</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>15772.77</t>
+          <t>15772770000</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>16100.269</t>
+          <t>16100269000</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>16307.196</t>
+          <t>16307196000</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>15704.182</t>
+          <t>15704182000</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16541.346</t>
+          <t>16541346000</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>16859.794</t>
+          <t>16859794000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>17063.268</t>
+          <t>17063268000</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>17138.589</t>
+          <t>17138589000</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>17498.639</t>
+          <t>17498639000</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>248493.695</t>
+          <t>248493695000</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>247634.371</t>
+          <t>247634371000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>245209.02</t>
+          <t>245209020000</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>242844.555</t>
+          <t>242844555000</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>245677.374</t>
+          <t>245677374000</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>249806.48</t>
+          <t>249806480000</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>254542.763</t>
+          <t>254542763000</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>256427.007</t>
+          <t>256427007000</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>255070.419</t>
+          <t>255070419000</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>241928.353</t>
+          <t>241928353000</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>242827.728</t>
+          <t>242827728000</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>247004.674</t>
+          <t>247004674000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>252068.151</t>
+          <t>252068151000</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>257055.775</t>
+          <t>257055775000</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>262614.229</t>
+          <t>262614229000</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>756644.638</t>
+          <t>756644638131.996</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>790526.622</t>
+          <t>790526621521.432</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>823145.14</t>
+          <t>823145139531.026</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>858848.102</t>
+          <t>858848101645.368</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>904228.799</t>
+          <t>904228799145.655</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>924304.549</t>
+          <t>924304548778.285</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>958428.493</t>
+          <t>958428493240.903</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>995552.657</t>
+          <t>995552657262.908</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>1035652.129</t>
+          <t>1035652128977.66</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>1057391.769</t>
+          <t>1057391769375.36</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1088507.47</t>
+          <t>1088507470062.05</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1158361.996</t>
+          <t>1158361995802.32</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1242666.113</t>
+          <t>1242666112900.78</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1328716.665</t>
+          <t>1328716664644.52</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1400688.27</t>
+          <t>1400688270047.93</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2809079.006</t>
+          <t>2809079006068.96</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2892064.697</t>
+          <t>2892064697228.51</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2973936.356</t>
+          <t>2973936356000.14</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>3054582.497</t>
+          <t>3054582496733.38</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>3160246.766</t>
+          <t>3160246765918.43</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3215876.111</t>
+          <t>3215876110843.66</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>3287171.254</t>
+          <t>3287171253516.98</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>3384123.972</t>
+          <t>3384123972341.74</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>3469604.887</t>
+          <t>3469604886766.92</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>3494833.016</t>
+          <t>3494833015568.45</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>3558445.83</t>
+          <t>3558445830322.22</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>3728988.968</t>
+          <t>3728988967927.7</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>3930840.896</t>
+          <t>3930840896316.45</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>4138111.091</t>
+          <t>4138111090504.92</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>4315651.405</t>
+          <t>4315651405372.53</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2414.731</t>
+          <t>2414731000</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2366.07</t>
+          <t>2366070000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2405.113</t>
+          <t>2405113000</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2483.917</t>
+          <t>2483917000</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2498.072</t>
+          <t>2498072000</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2536.244</t>
+          <t>2536244000</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2584.097</t>
+          <t>2584097000</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2651.114</t>
+          <t>2651114000</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2747.62</t>
+          <t>2747620000</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2730.066</t>
+          <t>2730066000</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2610.403</t>
+          <t>2610403000</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>2510.444</t>
+          <t>2510444000</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2443.903</t>
+          <t>2443903000</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2405.928</t>
+          <t>2405928000</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2489.511</t>
+          <t>2489511000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6057.222</t>
+          <t>6057222000</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6007.552</t>
+          <t>6007552000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>5970.524</t>
+          <t>5970524000</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>5982.301</t>
+          <t>5982301000</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>6094.74</t>
+          <t>6094740000</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>6098.211</t>
+          <t>6098211000</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>6189.574</t>
+          <t>6189574000</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>6325.867</t>
+          <t>6325867000</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>6443.864</t>
+          <t>6443864000</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>6348.042</t>
+          <t>6348042000</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>6370.689</t>
+          <t>6370689000</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>6497.347</t>
+          <t>6497347000</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>6534.815</t>
+          <t>6534815000</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>6536.929</t>
+          <t>6536929000</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>6628.596</t>
+          <t>6628596000</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3.045e+09</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3.005e+09</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2.987e+09</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2.926e+09</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2.99e+09</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3.049e+09</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>3.152e+09</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3.323e+09</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3.456e+09</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3.389e+09</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3.399e+09</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3.467e+09</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3.531e+09</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3.562e+09</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>3614</t>
+          <t>3.614e+09</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>hours_worked.empe.s.hr</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
